--- a/0_setup/4_define_samples.xlsx
+++ b/0_setup/4_define_samples.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/projects/mw2098/publications/2024_weilert_acc/code/0_setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A0676A-DE93-AB45-816B-9E9138410B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC943D56-D310-D745-833E-538CDFFC8ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32680" yWindow="-1100" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="samples_legacy" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="512">
   <si>
     <t>sample_name</t>
   </si>
@@ -1428,6 +1428,147 @@
   </si>
   <si>
     <t>Akr1cl_context_AB</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_atac_day0_1</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_atac_day0_2</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_atac_day4_1</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_atac_day4_2</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_atac_day8_1</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_atac_day8_2</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_atac_day12_1</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_atac_day12_2</t>
+  </si>
+  <si>
+    <t>published</t>
+  </si>
+  <si>
+    <t>mESC 129XC57BL/6J</t>
+  </si>
+  <si>
+    <t>day0_differentiation</t>
+  </si>
+  <si>
+    <t>day4_differentiation</t>
+  </si>
+  <si>
+    <t>day8_differentiation</t>
+  </si>
+  <si>
+    <t>day12_differentiation</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453496_1.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453496_2.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453490_1.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453490_2.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453495_1.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453495_2.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453491_1.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453491_2.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453486_1.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453486_2.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453481_1.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453481_2.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453493_1.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453493_2.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453494_1.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453494_2.fastq.gz</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_rna_day0_1</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_rna_day0_2</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_rna_day4_1</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_rna_day4_2</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_rna_day8_1</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_rna_day8_2</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_rna_day12_1</t>
+  </si>
+  <si>
+    <t>Bunina_mesc_rna_day12_2</t>
+  </si>
+  <si>
+    <t>RNA-seq</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453507.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453522.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453512.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453520.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453517.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453526.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453525.fastq.gz</t>
+  </si>
+  <si>
+    <t>/n/projects/mw2098/publications/2024_weilert_acc/public/published/Bunina_2020_CellSystems/fastq/ERR3453518.fastq.gz</t>
   </si>
 </sst>
 </file>
@@ -1933,11 +2074,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2293,7 +2435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z88"/>
+  <dimension ref="A1:Z104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="57.83203125" customWidth="1"/>
@@ -2302,7 +2444,7 @@
     <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="51.6640625" customWidth="1"/>
+    <col min="7" max="7" width="33" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.1640625" customWidth="1"/>
     <col min="10" max="10" width="32.1640625" customWidth="1"/>
@@ -2319,7 +2461,7 @@
     <col min="21" max="21" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.5" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="101.33203125" customWidth="1"/>
+    <col min="24" max="24" width="110.1640625" customWidth="1"/>
     <col min="25" max="25" width="83" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -8414,6 +8556,1070 @@
       </c>
       <c r="Z88" t="s">
         <v>459</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>465</v>
+      </c>
+      <c r="B89" t="s">
+        <v>46</v>
+      </c>
+      <c r="C89" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" t="s">
+        <v>43</v>
+      </c>
+      <c r="G89" t="s">
+        <v>465</v>
+      </c>
+      <c r="H89" t="s">
+        <v>473</v>
+      </c>
+      <c r="I89" t="s">
+        <v>27</v>
+      </c>
+      <c r="J89" t="s">
+        <v>27</v>
+      </c>
+      <c r="K89" t="s">
+        <v>11</v>
+      </c>
+      <c r="L89" t="s">
+        <v>474</v>
+      </c>
+      <c r="M89" t="s">
+        <v>475</v>
+      </c>
+      <c r="N89" t="s">
+        <v>38</v>
+      </c>
+      <c r="O89" t="s">
+        <v>238</v>
+      </c>
+      <c r="P89" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R89" t="s">
+        <v>238</v>
+      </c>
+      <c r="S89" t="s">
+        <v>241</v>
+      </c>
+      <c r="T89">
+        <v>1</v>
+      </c>
+      <c r="U89" t="s">
+        <v>11</v>
+      </c>
+      <c r="X89" t="s">
+        <v>479</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>466</v>
+      </c>
+      <c r="B90" t="s">
+        <v>46</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" t="s">
+        <v>43</v>
+      </c>
+      <c r="G90" t="s">
+        <v>466</v>
+      </c>
+      <c r="H90" t="s">
+        <v>473</v>
+      </c>
+      <c r="I90" t="s">
+        <v>27</v>
+      </c>
+      <c r="J90" t="s">
+        <v>27</v>
+      </c>
+      <c r="K90" t="s">
+        <v>11</v>
+      </c>
+      <c r="L90" t="s">
+        <v>474</v>
+      </c>
+      <c r="M90" t="s">
+        <v>475</v>
+      </c>
+      <c r="N90" t="s">
+        <v>38</v>
+      </c>
+      <c r="O90" t="s">
+        <v>238</v>
+      </c>
+      <c r="P90" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R90" t="s">
+        <v>238</v>
+      </c>
+      <c r="S90" t="s">
+        <v>241</v>
+      </c>
+      <c r="T90">
+        <v>1</v>
+      </c>
+      <c r="U90" t="s">
+        <v>11</v>
+      </c>
+      <c r="X90" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>467</v>
+      </c>
+      <c r="B91" t="s">
+        <v>46</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91" t="s">
+        <v>467</v>
+      </c>
+      <c r="H91" t="s">
+        <v>473</v>
+      </c>
+      <c r="I91" t="s">
+        <v>27</v>
+      </c>
+      <c r="J91" t="s">
+        <v>27</v>
+      </c>
+      <c r="K91" t="s">
+        <v>11</v>
+      </c>
+      <c r="L91" t="s">
+        <v>474</v>
+      </c>
+      <c r="M91" t="s">
+        <v>476</v>
+      </c>
+      <c r="N91" t="s">
+        <v>38</v>
+      </c>
+      <c r="O91" t="s">
+        <v>238</v>
+      </c>
+      <c r="P91" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R91" t="s">
+        <v>238</v>
+      </c>
+      <c r="S91" t="s">
+        <v>241</v>
+      </c>
+      <c r="T91">
+        <v>1</v>
+      </c>
+      <c r="U91" t="s">
+        <v>11</v>
+      </c>
+      <c r="X91" t="s">
+        <v>483</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>468</v>
+      </c>
+      <c r="B92" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" t="s">
+        <v>43</v>
+      </c>
+      <c r="G92" t="s">
+        <v>468</v>
+      </c>
+      <c r="H92" t="s">
+        <v>473</v>
+      </c>
+      <c r="I92" t="s">
+        <v>27</v>
+      </c>
+      <c r="J92" t="s">
+        <v>27</v>
+      </c>
+      <c r="K92" t="s">
+        <v>11</v>
+      </c>
+      <c r="L92" t="s">
+        <v>474</v>
+      </c>
+      <c r="M92" t="s">
+        <v>476</v>
+      </c>
+      <c r="N92" t="s">
+        <v>38</v>
+      </c>
+      <c r="O92" t="s">
+        <v>238</v>
+      </c>
+      <c r="P92" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R92" t="s">
+        <v>238</v>
+      </c>
+      <c r="S92" t="s">
+        <v>241</v>
+      </c>
+      <c r="T92">
+        <v>1</v>
+      </c>
+      <c r="U92" t="s">
+        <v>11</v>
+      </c>
+      <c r="X92" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>469</v>
+      </c>
+      <c r="B93" t="s">
+        <v>46</v>
+      </c>
+      <c r="C93" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" t="s">
+        <v>469</v>
+      </c>
+      <c r="H93" t="s">
+        <v>473</v>
+      </c>
+      <c r="I93" t="s">
+        <v>27</v>
+      </c>
+      <c r="J93" t="s">
+        <v>27</v>
+      </c>
+      <c r="K93" t="s">
+        <v>11</v>
+      </c>
+      <c r="L93" t="s">
+        <v>474</v>
+      </c>
+      <c r="M93" t="s">
+        <v>477</v>
+      </c>
+      <c r="N93" t="s">
+        <v>38</v>
+      </c>
+      <c r="O93" t="s">
+        <v>238</v>
+      </c>
+      <c r="P93" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R93" t="s">
+        <v>238</v>
+      </c>
+      <c r="S93" t="s">
+        <v>241</v>
+      </c>
+      <c r="T93">
+        <v>1</v>
+      </c>
+      <c r="U93" t="s">
+        <v>11</v>
+      </c>
+      <c r="X93" t="s">
+        <v>487</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>470</v>
+      </c>
+      <c r="B94" t="s">
+        <v>46</v>
+      </c>
+      <c r="C94" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" t="s">
+        <v>43</v>
+      </c>
+      <c r="G94" t="s">
+        <v>470</v>
+      </c>
+      <c r="H94" t="s">
+        <v>473</v>
+      </c>
+      <c r="I94" t="s">
+        <v>27</v>
+      </c>
+      <c r="J94" t="s">
+        <v>27</v>
+      </c>
+      <c r="K94" t="s">
+        <v>11</v>
+      </c>
+      <c r="L94" t="s">
+        <v>474</v>
+      </c>
+      <c r="M94" t="s">
+        <v>477</v>
+      </c>
+      <c r="N94" t="s">
+        <v>38</v>
+      </c>
+      <c r="O94" t="s">
+        <v>238</v>
+      </c>
+      <c r="P94" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R94" t="s">
+        <v>238</v>
+      </c>
+      <c r="S94" t="s">
+        <v>241</v>
+      </c>
+      <c r="T94">
+        <v>1</v>
+      </c>
+      <c r="U94" t="s">
+        <v>11</v>
+      </c>
+      <c r="X94" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>471</v>
+      </c>
+      <c r="B95" t="s">
+        <v>46</v>
+      </c>
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" t="s">
+        <v>43</v>
+      </c>
+      <c r="G95" t="s">
+        <v>471</v>
+      </c>
+      <c r="H95" t="s">
+        <v>473</v>
+      </c>
+      <c r="I95" t="s">
+        <v>27</v>
+      </c>
+      <c r="J95" t="s">
+        <v>27</v>
+      </c>
+      <c r="K95" t="s">
+        <v>11</v>
+      </c>
+      <c r="L95" t="s">
+        <v>474</v>
+      </c>
+      <c r="M95" t="s">
+        <v>478</v>
+      </c>
+      <c r="N95" t="s">
+        <v>38</v>
+      </c>
+      <c r="O95" t="s">
+        <v>238</v>
+      </c>
+      <c r="P95" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R95" t="s">
+        <v>238</v>
+      </c>
+      <c r="S95" t="s">
+        <v>241</v>
+      </c>
+      <c r="T95">
+        <v>1</v>
+      </c>
+      <c r="U95" t="s">
+        <v>11</v>
+      </c>
+      <c r="X95" t="s">
+        <v>491</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>472</v>
+      </c>
+      <c r="B96" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" t="s">
+        <v>43</v>
+      </c>
+      <c r="G96" t="s">
+        <v>472</v>
+      </c>
+      <c r="H96" t="s">
+        <v>473</v>
+      </c>
+      <c r="I96" t="s">
+        <v>27</v>
+      </c>
+      <c r="J96" t="s">
+        <v>27</v>
+      </c>
+      <c r="K96" t="s">
+        <v>11</v>
+      </c>
+      <c r="L96" t="s">
+        <v>474</v>
+      </c>
+      <c r="M96" t="s">
+        <v>478</v>
+      </c>
+      <c r="N96" t="s">
+        <v>38</v>
+      </c>
+      <c r="O96" t="s">
+        <v>238</v>
+      </c>
+      <c r="P96" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q96" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R96" t="s">
+        <v>238</v>
+      </c>
+      <c r="S96" t="s">
+        <v>241</v>
+      </c>
+      <c r="T96">
+        <v>1</v>
+      </c>
+      <c r="U96" t="s">
+        <v>11</v>
+      </c>
+      <c r="X96" t="s">
+        <v>493</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>495</v>
+      </c>
+      <c r="B97" t="s">
+        <v>46</v>
+      </c>
+      <c r="C97" t="s">
+        <v>32</v>
+      </c>
+      <c r="D97" t="s">
+        <v>503</v>
+      </c>
+      <c r="E97" t="s">
+        <v>321</v>
+      </c>
+      <c r="G97" t="s">
+        <v>495</v>
+      </c>
+      <c r="H97" t="s">
+        <v>473</v>
+      </c>
+      <c r="I97" t="s">
+        <v>27</v>
+      </c>
+      <c r="J97" t="s">
+        <v>27</v>
+      </c>
+      <c r="K97" t="s">
+        <v>11</v>
+      </c>
+      <c r="L97" t="s">
+        <v>474</v>
+      </c>
+      <c r="M97" t="s">
+        <v>475</v>
+      </c>
+      <c r="N97" t="s">
+        <v>284</v>
+      </c>
+      <c r="O97" t="s">
+        <v>238</v>
+      </c>
+      <c r="P97" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q97" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R97" t="s">
+        <v>238</v>
+      </c>
+      <c r="S97" t="s">
+        <v>241</v>
+      </c>
+      <c r="T97">
+        <v>1</v>
+      </c>
+      <c r="U97" t="s">
+        <v>11</v>
+      </c>
+      <c r="X97" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>496</v>
+      </c>
+      <c r="B98" t="s">
+        <v>46</v>
+      </c>
+      <c r="C98" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" t="s">
+        <v>503</v>
+      </c>
+      <c r="E98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G98" t="s">
+        <v>496</v>
+      </c>
+      <c r="H98" t="s">
+        <v>473</v>
+      </c>
+      <c r="I98" t="s">
+        <v>27</v>
+      </c>
+      <c r="J98" t="s">
+        <v>27</v>
+      </c>
+      <c r="K98" t="s">
+        <v>11</v>
+      </c>
+      <c r="L98" t="s">
+        <v>474</v>
+      </c>
+      <c r="M98" t="s">
+        <v>475</v>
+      </c>
+      <c r="N98" t="s">
+        <v>284</v>
+      </c>
+      <c r="O98" t="s">
+        <v>238</v>
+      </c>
+      <c r="P98" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R98" t="s">
+        <v>238</v>
+      </c>
+      <c r="S98" t="s">
+        <v>241</v>
+      </c>
+      <c r="T98">
+        <v>1</v>
+      </c>
+      <c r="U98" t="s">
+        <v>11</v>
+      </c>
+      <c r="X98" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>497</v>
+      </c>
+      <c r="B99" t="s">
+        <v>46</v>
+      </c>
+      <c r="C99" t="s">
+        <v>32</v>
+      </c>
+      <c r="D99" t="s">
+        <v>503</v>
+      </c>
+      <c r="E99" t="s">
+        <v>321</v>
+      </c>
+      <c r="G99" t="s">
+        <v>497</v>
+      </c>
+      <c r="H99" t="s">
+        <v>473</v>
+      </c>
+      <c r="I99" t="s">
+        <v>27</v>
+      </c>
+      <c r="J99" t="s">
+        <v>27</v>
+      </c>
+      <c r="K99" t="s">
+        <v>11</v>
+      </c>
+      <c r="L99" t="s">
+        <v>474</v>
+      </c>
+      <c r="M99" t="s">
+        <v>476</v>
+      </c>
+      <c r="N99" t="s">
+        <v>284</v>
+      </c>
+      <c r="O99" t="s">
+        <v>238</v>
+      </c>
+      <c r="P99" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q99" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R99" t="s">
+        <v>238</v>
+      </c>
+      <c r="S99" t="s">
+        <v>241</v>
+      </c>
+      <c r="T99">
+        <v>1</v>
+      </c>
+      <c r="U99" t="s">
+        <v>11</v>
+      </c>
+      <c r="X99" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>498</v>
+      </c>
+      <c r="B100" t="s">
+        <v>46</v>
+      </c>
+      <c r="C100" t="s">
+        <v>32</v>
+      </c>
+      <c r="D100" t="s">
+        <v>503</v>
+      </c>
+      <c r="E100" t="s">
+        <v>321</v>
+      </c>
+      <c r="G100" t="s">
+        <v>498</v>
+      </c>
+      <c r="H100" t="s">
+        <v>473</v>
+      </c>
+      <c r="I100" t="s">
+        <v>27</v>
+      </c>
+      <c r="J100" t="s">
+        <v>27</v>
+      </c>
+      <c r="K100" t="s">
+        <v>11</v>
+      </c>
+      <c r="L100" t="s">
+        <v>474</v>
+      </c>
+      <c r="M100" t="s">
+        <v>476</v>
+      </c>
+      <c r="N100" t="s">
+        <v>284</v>
+      </c>
+      <c r="O100" t="s">
+        <v>238</v>
+      </c>
+      <c r="P100" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q100" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R100" t="s">
+        <v>238</v>
+      </c>
+      <c r="S100" t="s">
+        <v>241</v>
+      </c>
+      <c r="T100">
+        <v>1</v>
+      </c>
+      <c r="U100" t="s">
+        <v>11</v>
+      </c>
+      <c r="X100" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>499</v>
+      </c>
+      <c r="B101" t="s">
+        <v>46</v>
+      </c>
+      <c r="C101" t="s">
+        <v>32</v>
+      </c>
+      <c r="D101" t="s">
+        <v>503</v>
+      </c>
+      <c r="E101" t="s">
+        <v>321</v>
+      </c>
+      <c r="G101" t="s">
+        <v>499</v>
+      </c>
+      <c r="H101" t="s">
+        <v>473</v>
+      </c>
+      <c r="I101" t="s">
+        <v>27</v>
+      </c>
+      <c r="J101" t="s">
+        <v>27</v>
+      </c>
+      <c r="K101" t="s">
+        <v>11</v>
+      </c>
+      <c r="L101" t="s">
+        <v>474</v>
+      </c>
+      <c r="M101" t="s">
+        <v>477</v>
+      </c>
+      <c r="N101" t="s">
+        <v>284</v>
+      </c>
+      <c r="O101" t="s">
+        <v>238</v>
+      </c>
+      <c r="P101" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R101" t="s">
+        <v>238</v>
+      </c>
+      <c r="S101" t="s">
+        <v>241</v>
+      </c>
+      <c r="T101">
+        <v>1</v>
+      </c>
+      <c r="U101" t="s">
+        <v>11</v>
+      </c>
+      <c r="X101" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>500</v>
+      </c>
+      <c r="B102" t="s">
+        <v>46</v>
+      </c>
+      <c r="C102" t="s">
+        <v>32</v>
+      </c>
+      <c r="D102" t="s">
+        <v>503</v>
+      </c>
+      <c r="E102" t="s">
+        <v>321</v>
+      </c>
+      <c r="G102" t="s">
+        <v>500</v>
+      </c>
+      <c r="H102" t="s">
+        <v>473</v>
+      </c>
+      <c r="I102" t="s">
+        <v>27</v>
+      </c>
+      <c r="J102" t="s">
+        <v>27</v>
+      </c>
+      <c r="K102" t="s">
+        <v>11</v>
+      </c>
+      <c r="L102" t="s">
+        <v>474</v>
+      </c>
+      <c r="M102" t="s">
+        <v>477</v>
+      </c>
+      <c r="N102" t="s">
+        <v>284</v>
+      </c>
+      <c r="O102" t="s">
+        <v>238</v>
+      </c>
+      <c r="P102" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q102" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R102" t="s">
+        <v>238</v>
+      </c>
+      <c r="S102" t="s">
+        <v>241</v>
+      </c>
+      <c r="T102">
+        <v>1</v>
+      </c>
+      <c r="U102" t="s">
+        <v>11</v>
+      </c>
+      <c r="X102" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>501</v>
+      </c>
+      <c r="B103" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" t="s">
+        <v>32</v>
+      </c>
+      <c r="D103" t="s">
+        <v>503</v>
+      </c>
+      <c r="E103" t="s">
+        <v>321</v>
+      </c>
+      <c r="G103" t="s">
+        <v>501</v>
+      </c>
+      <c r="H103" t="s">
+        <v>473</v>
+      </c>
+      <c r="I103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K103" t="s">
+        <v>11</v>
+      </c>
+      <c r="L103" t="s">
+        <v>474</v>
+      </c>
+      <c r="M103" t="s">
+        <v>478</v>
+      </c>
+      <c r="N103" t="s">
+        <v>284</v>
+      </c>
+      <c r="O103" t="s">
+        <v>238</v>
+      </c>
+      <c r="P103" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q103" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R103" t="s">
+        <v>238</v>
+      </c>
+      <c r="S103" t="s">
+        <v>241</v>
+      </c>
+      <c r="T103">
+        <v>1</v>
+      </c>
+      <c r="U103" t="s">
+        <v>11</v>
+      </c>
+      <c r="X103" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>502</v>
+      </c>
+      <c r="B104" t="s">
+        <v>46</v>
+      </c>
+      <c r="C104" t="s">
+        <v>32</v>
+      </c>
+      <c r="D104" t="s">
+        <v>503</v>
+      </c>
+      <c r="E104" t="s">
+        <v>321</v>
+      </c>
+      <c r="G104" t="s">
+        <v>502</v>
+      </c>
+      <c r="H104" t="s">
+        <v>473</v>
+      </c>
+      <c r="I104" t="s">
+        <v>27</v>
+      </c>
+      <c r="J104" t="s">
+        <v>27</v>
+      </c>
+      <c r="K104" t="s">
+        <v>11</v>
+      </c>
+      <c r="L104" t="s">
+        <v>474</v>
+      </c>
+      <c r="M104" t="s">
+        <v>478</v>
+      </c>
+      <c r="N104" t="s">
+        <v>284</v>
+      </c>
+      <c r="O104" t="s">
+        <v>238</v>
+      </c>
+      <c r="P104" s="4">
+        <v>44006</v>
+      </c>
+      <c r="Q104" s="4">
+        <v>44006</v>
+      </c>
+      <c r="R104" t="s">
+        <v>238</v>
+      </c>
+      <c r="S104" t="s">
+        <v>241</v>
+      </c>
+      <c r="T104">
+        <v>1</v>
+      </c>
+      <c r="U104" t="s">
+        <v>11</v>
+      </c>
+      <c r="X104" t="s">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
